--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_o_higgins.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.79030672726948</v>
+      </c>
+      <c r="C2">
         <v>26.12632469365994</v>
-      </c>
-      <c r="C2">
-        <v>28.79030672726948</v>
       </c>
       <c r="D2">
         <v>3.827557116147567</v>
       </c>
       <c r="E2">
-        <v>16.86476426321922</v>
+        <v>18.58438726894488</v>
       </c>
       <c r="F2">
         <v>64.55084846783591</v>
       </c>
       <c r="G2">
-        <v>18.58438726894488</v>
+        <v>16.86476426321922</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.40249522310891</v>
+      </c>
+      <c r="C3">
         <v>27.23389906710127</v>
-      </c>
-      <c r="C3">
-        <v>27.40249522310891</v>
       </c>
       <c r="D3">
         <v>3.671894345852249</v>
       </c>
       <c r="E3">
-        <v>17.61157144933856</v>
+        <v>17.72059892426225</v>
       </c>
       <c r="F3">
         <v>64.66782962639918</v>
       </c>
       <c r="G3">
-        <v>17.72059892426224</v>
+        <v>17.61157144933857</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.85996409335727</v>
+      </c>
+      <c r="C4">
         <v>35.72710951526032</v>
-      </c>
-      <c r="C4">
-        <v>28.85996409335727</v>
       </c>
       <c r="D4">
         <v>2.798994974874372</v>
       </c>
       <c r="E4">
-        <v>21.70711753476957</v>
+        <v>17.53476956640306</v>
       </c>
       <c r="F4">
         <v>60.75811289882738</v>
       </c>
       <c r="G4">
-        <v>17.53476956640305</v>
+        <v>21.70711753476957</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.93800620694876</v>
+      </c>
+      <c r="C5">
         <v>31.09529937173567</v>
-      </c>
-      <c r="C5">
-        <v>28.93800620694876</v>
       </c>
       <c r="D5">
         <v>3.215920155793574</v>
       </c>
       <c r="E5">
-        <v>19.43051745341027</v>
+        <v>18.08248983066881</v>
       </c>
       <c r="F5">
         <v>62.48699271592091</v>
       </c>
       <c r="G5">
-        <v>18.08248983066881</v>
+        <v>19.43051745341027</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>32.01383268339342</v>
+      </c>
+      <c r="C6">
         <v>28.76168052387609</v>
-      </c>
-      <c r="C6">
-        <v>32.01383268339342</v>
       </c>
       <c r="D6">
         <v>3.476848298797647</v>
       </c>
       <c r="E6">
-        <v>17.88934144890394</v>
+        <v>19.91213216786417</v>
       </c>
       <c r="F6">
         <v>62.19852638323189</v>
       </c>
       <c r="G6">
-        <v>19.91213216786417</v>
+        <v>17.88934144890394</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>32.00796989152092</v>
+      </c>
+      <c r="C7">
         <v>24.13991587336728</v>
-      </c>
-      <c r="C7">
-        <v>32.00796989152092</v>
       </c>
       <c r="D7">
         <v>4.142516507703595</v>
       </c>
       <c r="E7">
-        <v>15.45964952078489</v>
+        <v>20.49849713605172</v>
       </c>
       <c r="F7">
         <v>64.04185334316338</v>
       </c>
       <c r="G7">
-        <v>20.49849713605172</v>
+        <v>15.45964952078489</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.82554168994847</v>
+      </c>
+      <c r="C8">
         <v>29.98696219035202</v>
-      </c>
-      <c r="C8">
-        <v>29.82554168994847</v>
       </c>
       <c r="D8">
         <v>3.334782608695652</v>
       </c>
       <c r="E8">
-        <v>18.763839788664</v>
+        <v>18.6628336117478</v>
       </c>
       <c r="F8">
         <v>62.57332659958821</v>
       </c>
       <c r="G8">
-        <v>18.6628336117478</v>
+        <v>18.763839788664</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>35.83612549497411</v>
+      </c>
+      <c r="C9">
         <v>21.30673164788303</v>
-      </c>
-      <c r="C9">
-        <v>35.83612549497411</v>
       </c>
       <c r="D9">
         <v>4.693352394567548</v>
       </c>
       <c r="E9">
-        <v>13.55882923047102</v>
+        <v>22.80480713316534</v>
       </c>
       <c r="F9">
         <v>63.63636363636364</v>
       </c>
       <c r="G9">
-        <v>22.80480713316534</v>
+        <v>13.55882923047102</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.31578947368421</v>
+      </c>
+      <c r="C10">
         <v>31.95006747638326</v>
-      </c>
-      <c r="C10">
-        <v>26.31578947368421</v>
       </c>
       <c r="D10">
         <v>3.129883843717001</v>
       </c>
       <c r="E10">
-        <v>20.18759326369644</v>
+        <v>16.62758473672991</v>
       </c>
       <c r="F10">
         <v>63.18482199957365</v>
       </c>
       <c r="G10">
-        <v>16.62758473672991</v>
+        <v>20.18759326369644</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>32.03690303907381</v>
+      </c>
+      <c r="C11">
         <v>27.14664737095996</v>
-      </c>
-      <c r="C11">
-        <v>32.03690303907381</v>
       </c>
       <c r="D11">
         <v>3.683696135051088</v>
       </c>
       <c r="E11">
-        <v>17.0536762756165</v>
+        <v>20.12576233948256</v>
       </c>
       <c r="F11">
         <v>62.82056138490094</v>
       </c>
       <c r="G11">
-        <v>20.12576233948256</v>
+        <v>17.0536762756165</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.67734830965752</v>
+      </c>
+      <c r="C12">
         <v>27.10053958815109</v>
-      </c>
-      <c r="C12">
-        <v>29.67734830965752</v>
       </c>
       <c r="D12">
         <v>3.689963429500203</v>
       </c>
       <c r="E12">
-        <v>17.2859450726979</v>
+        <v>18.92954976469762</v>
       </c>
       <c r="F12">
         <v>63.78450516260448</v>
       </c>
       <c r="G12">
-        <v>18.92954976469762</v>
+        <v>17.2859450726979</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.91899915182358</v>
+      </c>
+      <c r="C13">
         <v>30.43893129770992</v>
-      </c>
-      <c r="C13">
-        <v>26.91899915182358</v>
       </c>
       <c r="D13">
         <v>3.285266457680251</v>
       </c>
       <c r="E13">
-        <v>19.34375421102277</v>
+        <v>17.10685891389301</v>
       </c>
       <c r="F13">
         <v>63.54938687508422</v>
       </c>
       <c r="G13">
-        <v>17.10685891389301</v>
+        <v>19.34375421102277</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.64309818415555</v>
+      </c>
+      <c r="C14">
         <v>32.7896512935883</v>
-      </c>
-      <c r="C14">
-        <v>26.64309818415555</v>
       </c>
       <c r="D14">
         <v>3.049742710120069</v>
       </c>
       <c r="E14">
-        <v>20.56644660585597</v>
+        <v>16.71118278486116</v>
       </c>
       <c r="F14">
         <v>62.72237060928288</v>
       </c>
       <c r="G14">
-        <v>16.71118278486116</v>
+        <v>20.56644660585597</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.25919016789202</v>
+      </c>
+      <c r="C15">
         <v>29.24393723252496</v>
-      </c>
-      <c r="C15">
-        <v>26.25919016789202</v>
       </c>
       <c r="D15">
         <v>3.419512195121951</v>
       </c>
       <c r="E15">
-        <v>18.80601227859713</v>
+        <v>16.88659939312681</v>
       </c>
       <c r="F15">
         <v>64.30738832827606</v>
       </c>
       <c r="G15">
-        <v>16.88659939312681</v>
+        <v>18.80601227859713</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>29.19189596586699</v>
+      </c>
+      <c r="C16">
         <v>26.94616897882016</v>
-      </c>
-      <c r="C16">
-        <v>29.19189596586699</v>
       </c>
       <c r="D16">
         <v>3.711102683227458</v>
       </c>
       <c r="E16">
-        <v>17.25791144418627</v>
+        <v>18.69620708839219</v>
       </c>
       <c r="F16">
         <v>64.04588146742154</v>
       </c>
       <c r="G16">
-        <v>18.69620708839219</v>
+        <v>17.25791144418627</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>28.76401012344404</v>
+      </c>
+      <c r="C17">
         <v>23.86240380145654</v>
-      </c>
-      <c r="C17">
-        <v>28.76401012344404</v>
       </c>
       <c r="D17">
         <v>4.190692640692641</v>
       </c>
       <c r="E17">
-        <v>15.63451776649746</v>
+        <v>18.84602368866328</v>
       </c>
       <c r="F17">
         <v>65.51945854483925</v>
       </c>
       <c r="G17">
-        <v>18.84602368866328</v>
+        <v>15.63451776649746</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>29.41578174616724</v>
+      </c>
+      <c r="C18">
         <v>32.06883600232185</v>
-      </c>
-      <c r="C18">
-        <v>29.41578174616724</v>
       </c>
       <c r="D18">
         <v>3.118292163543441</v>
       </c>
       <c r="E18">
-        <v>19.85875586755191</v>
+        <v>18.21584133293864</v>
       </c>
       <c r="F18">
         <v>61.92540279950946</v>
       </c>
       <c r="G18">
-        <v>18.21584133293864</v>
+        <v>19.85875586755191</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>25.69935691318328</v>
+      </c>
+      <c r="C19">
         <v>28.39228295819936</v>
-      </c>
-      <c r="C19">
-        <v>25.69935691318328</v>
       </c>
       <c r="D19">
         <v>3.522083805209513</v>
       </c>
       <c r="E19">
-        <v>18.42558297250769</v>
+        <v>16.67796963847879</v>
       </c>
       <c r="F19">
-        <v>64.8964473890135</v>
+        <v>64.89644738901352</v>
       </c>
       <c r="G19">
-        <v>16.67796963847879</v>
+        <v>18.4255829725077</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>27.23381487426431</v>
+      </c>
+      <c r="C20">
         <v>42.37560192616372</v>
-      </c>
-      <c r="C20">
-        <v>27.23381487426431</v>
       </c>
       <c r="D20">
         <v>2.359848484848485</v>
       </c>
       <c r="E20">
+        <v>16.05678233438486</v>
+      </c>
+      <c r="F20">
+        <v>58.9589905362776</v>
+      </c>
+      <c r="G20">
         <v>24.98422712933754</v>
-      </c>
-      <c r="F20">
-        <v>58.95899053627761</v>
-      </c>
-      <c r="G20">
-        <v>16.05678233438486</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.80885780885781</v>
+      </c>
+      <c r="C21">
         <v>35.05827505827506</v>
-      </c>
-      <c r="C21">
-        <v>27.80885780885781</v>
       </c>
       <c r="D21">
         <v>2.852393617021276</v>
       </c>
       <c r="E21">
-        <v>21.52569056819808</v>
+        <v>17.07456705309861</v>
       </c>
       <c r="F21">
         <v>61.39974237870331</v>
       </c>
       <c r="G21">
-        <v>17.07456705309861</v>
+        <v>21.52569056819808</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>21.64035425490951</v>
+      </c>
+      <c r="C22">
         <v>33.63496341932999</v>
-      </c>
-      <c r="C22">
-        <v>21.64035425490951</v>
       </c>
       <c r="D22">
         <v>2.973096737263881</v>
       </c>
       <c r="E22">
+        <v>13.93676379417235</v>
+      </c>
+      <c r="F22">
+        <v>64.40173589584626</v>
+      </c>
+      <c r="G22">
         <v>21.6615003099814</v>
-      </c>
-      <c r="F22">
-        <v>64.40173589584624</v>
-      </c>
-      <c r="G22">
-        <v>13.93676379417235</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>30.75984131827891</v>
+      </c>
+      <c r="C23">
         <v>52.60909368324688</v>
-      </c>
-      <c r="C23">
-        <v>30.75984131827891</v>
       </c>
       <c r="D23">
         <v>1.900812064965197</v>
       </c>
       <c r="E23">
-        <v>28.69029788650358</v>
+        <v>16.77483774338492</v>
       </c>
       <c r="F23">
         <v>54.5348643701115</v>
       </c>
       <c r="G23">
-        <v>16.77483774338492</v>
+        <v>28.69029788650358</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>22.36118059029515</v>
+      </c>
+      <c r="C24">
         <v>41.34567283641821</v>
-      </c>
-      <c r="C24">
-        <v>22.36118059029515</v>
       </c>
       <c r="D24">
         <v>2.418632788868723</v>
       </c>
       <c r="E24">
-        <v>25.2559205500382</v>
+        <v>13.65928189457601</v>
       </c>
       <c r="F24">
-        <v>61.0847975553858</v>
+        <v>61.08479755538579</v>
       </c>
       <c r="G24">
-        <v>13.65928189457602</v>
+        <v>25.25592055003819</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.18272444731133</v>
+      </c>
+      <c r="C25">
         <v>26.5544674446334</v>
-      </c>
-      <c r="C25">
-        <v>28.18272444731133</v>
       </c>
       <c r="D25">
         <v>3.765844681634155</v>
       </c>
       <c r="E25">
-        <v>17.16101159647306</v>
+        <v>18.21328415148682</v>
       </c>
       <c r="F25">
         <v>64.62570425204012</v>
       </c>
       <c r="G25">
-        <v>18.21328415148682</v>
+        <v>17.16101159647306</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>31.58321743161799</v>
+      </c>
+      <c r="C26">
         <v>35.96430227167362</v>
-      </c>
-      <c r="C26">
-        <v>31.58321743161799</v>
       </c>
       <c r="D26">
         <v>2.780534966161779</v>
       </c>
       <c r="E26">
-        <v>21.46513558384062</v>
+        <v>18.85030437188711</v>
       </c>
       <c r="F26">
         <v>59.68456004427228</v>
       </c>
       <c r="G26">
-        <v>18.85030437188711</v>
+        <v>21.46513558384062</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.26375508456433</v>
+      </c>
+      <c r="C27">
         <v>28.18668379362021</v>
-      </c>
-      <c r="C27">
-        <v>28.26375508456433</v>
       </c>
       <c r="D27">
         <v>3.547774570864348</v>
       </c>
       <c r="E27">
-        <v>18.01636607460522</v>
+        <v>18.06562850652727</v>
       </c>
       <c r="F27">
         <v>63.91800541886751</v>
       </c>
       <c r="G27">
-        <v>18.06562850652727</v>
+        <v>18.01636607460522</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>26.2782401902497</v>
+      </c>
+      <c r="C28">
         <v>38.5731272294887</v>
-      </c>
-      <c r="C28">
-        <v>26.2782401902497</v>
       </c>
       <c r="D28">
         <v>2.592478421701603</v>
       </c>
       <c r="E28">
-        <v>23.39873052510098</v>
+        <v>15.94056549336411</v>
       </c>
       <c r="F28">
         <v>60.66070398153491</v>
       </c>
       <c r="G28">
-        <v>15.94056549336411</v>
+        <v>23.39873052510098</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>29.8941798941799</v>
+      </c>
+      <c r="C29">
         <v>30.01277139208174</v>
-      </c>
-      <c r="C29">
-        <v>29.8941798941799</v>
       </c>
       <c r="D29">
         <v>3.331914893617021</v>
       </c>
       <c r="E29">
-        <v>18.76889725597581</v>
+        <v>18.69473444007074</v>
       </c>
       <c r="F29">
         <v>62.53636830395345</v>
       </c>
       <c r="G29">
-        <v>18.69473444007074</v>
+        <v>18.76889725597581</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.11677565728013</v>
+      </c>
+      <c r="C30">
         <v>32.10996930468437</v>
-      </c>
-      <c r="C30">
-        <v>25.11677565728013</v>
       </c>
       <c r="D30">
         <v>3.114297589359933</v>
       </c>
       <c r="E30">
-        <v>20.4227145403616</v>
+        <v>15.97487479840421</v>
       </c>
       <c r="F30">
         <v>63.60241066123419</v>
       </c>
       <c r="G30">
-        <v>15.97487479840421</v>
+        <v>20.4227145403616</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>26.32553219621843</v>
+      </c>
+      <c r="C31">
         <v>32.19621843183922</v>
-      </c>
-      <c r="C31">
-        <v>26.32553219621843</v>
       </c>
       <c r="D31">
         <v>3.105954825462012</v>
       </c>
       <c r="E31">
-        <v>20.31028442739178</v>
+        <v>16.60688964884477</v>
       </c>
       <c r="F31">
         <v>63.08282592376345</v>
       </c>
       <c r="G31">
-        <v>16.60688964884477</v>
+        <v>20.31028442739178</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.15016247648367</v>
+      </c>
+      <c r="C32">
         <v>30.30613990080383</v>
-      </c>
-      <c r="C32">
-        <v>26.15016247648367</v>
       </c>
       <c r="D32">
         <v>3.299661399548533</v>
       </c>
       <c r="E32">
-        <v>19.37035417577613</v>
+        <v>16.71403585483166</v>
       </c>
       <c r="F32">
         <v>63.91560996939221</v>
       </c>
       <c r="G32">
-        <v>16.71403585483166</v>
+        <v>19.37035417577613</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>25.04911591355599</v>
+      </c>
+      <c r="C33">
         <v>47.05304518664047</v>
-      </c>
-      <c r="C33">
-        <v>25.04911591355599</v>
       </c>
       <c r="D33">
         <v>2.125260960334029</v>
       </c>
       <c r="E33">
-        <v>27.34018264840183</v>
+        <v>14.55479452054794</v>
       </c>
       <c r="F33">
         <v>58.10502283105023</v>
       </c>
       <c r="G33">
-        <v>14.55479452054794</v>
+        <v>27.34018264840183</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>27.0200583930535</v>
+      </c>
+      <c r="C34">
         <v>28.73772418761612</v>
-      </c>
-      <c r="C34">
-        <v>27.0200583930535</v>
       </c>
       <c r="D34">
         <v>3.479746668425914</v>
       </c>
       <c r="E34">
+        <v>17.34748527192171</v>
+      </c>
+      <c r="F34">
+        <v>64.20224937922977</v>
+      </c>
+      <c r="G34">
         <v>18.45026534884853</v>
-      </c>
-      <c r="F34">
-        <v>64.20224937922976</v>
-      </c>
-      <c r="G34">
-        <v>17.34748527192171</v>
       </c>
     </row>
   </sheetData>
